--- a/docs/培训/OpenWorker培训/01-质量周报/检验记录-机加车间.xlsx
+++ b/docs/培训/OpenWorker培训/01-质量周报/检验记录-机加车间.xlsx
@@ -506,11 +506,11 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P39J001</t>
+          <t>P40J001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -560,11 +560,11 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P39J002</t>
+          <t>P40J002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -606,11 +606,11 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P39J003</t>
+          <t>P40J003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -652,11 +652,11 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P39J004</t>
+          <t>P40J004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,11 +698,11 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P39J005</t>
+          <t>P40J005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -744,11 +744,11 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P39J006</t>
+          <t>P40J006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,11 +798,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P39J007</t>
+          <t>P40J007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -852,11 +852,11 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P39J008</t>
+          <t>P40J008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -898,11 +898,11 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P39J009</t>
+          <t>P40J009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -944,11 +944,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P39J010</t>
+          <t>P40J010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -990,11 +990,11 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P39J011</t>
+          <t>P40J011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1036,11 +1036,11 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P39J012</t>
+          <t>P40J012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1090,11 +1090,11 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P39J013</t>
+          <t>P40J013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1136,11 +1136,11 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P39J014</t>
+          <t>P40J014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1182,11 +1182,11 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P39J015</t>
+          <t>P40J015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1228,11 +1228,11 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P39J016</t>
+          <t>P40J016</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1282,11 +1282,11 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P39J017</t>
+          <t>P40J017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1336,11 +1336,11 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P39J018</t>
+          <t>P40J018</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1382,11 +1382,11 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P39J019</t>
+          <t>P40J019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1428,11 +1428,11 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P39J020</t>
+          <t>P40J020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1474,11 +1474,11 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P39J021</t>
+          <t>P40J021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1528,11 +1528,11 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P39J022</t>
+          <t>P40J022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1574,11 +1574,11 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P39J023</t>
+          <t>P40J023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1620,11 +1620,11 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P39J024</t>
+          <t>P40J024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1666,11 +1666,11 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P39J025</t>
+          <t>P40J025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
